--- a/연구코드/aec/results/신촌/linear_results.xlsx
+++ b/연구코드/aec/results/신촌/linear_results.xlsx
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5423</v>
+        <v>0.498</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0541</v>
+        <v>0.0689</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9598</v>
+        <v>0.9691</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.0341</v>
+        <v>1.9552</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/연구코드/aec/results/신촌/linear_results.xlsx
+++ b/연구코드/aec/results/신촌/linear_results.xlsx
@@ -484,28 +484,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.5075</v>
+        <v>43.5908</v>
       </c>
       <c r="C2" t="n">
-        <v>41.081</v>
+        <v>41.1706</v>
       </c>
       <c r="D2" t="n">
-        <v>45.934</v>
+        <v>46.0111</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2369</v>
+        <v>1.2337</v>
       </c>
       <c r="F2" t="n">
-        <v>35.1761</v>
+        <v>35.3347</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4949</v>
+        <v>0.4963</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4945</v>
+        <v>0.4959</v>
       </c>
     </row>
     <row r="3">
@@ -515,28 +515,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.5411</v>
+        <v>-2.3588</v>
       </c>
       <c r="C3" t="n">
-        <v>-4.2424</v>
+        <v>-4.0589</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.8399</v>
+        <v>-0.6586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8672</v>
+        <v>0.8666</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9304</v>
+        <v>-2.7219</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003447</v>
+        <v>0.00658</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0068</v>
+        <v>0.0058</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="4">
@@ -546,28 +546,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.7203</v>
+        <v>7.5579</v>
       </c>
       <c r="C4" t="n">
-        <v>6.0673</v>
+        <v>5.9045</v>
       </c>
       <c r="D4" t="n">
-        <v>9.373200000000001</v>
+        <v>9.211399999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8426</v>
+        <v>0.8428</v>
       </c>
       <c r="F4" t="n">
-        <v>9.1629</v>
+        <v>8.967599999999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0623</v>
+        <v>0.0597</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0616</v>
+        <v>0.0589</v>
       </c>
     </row>
     <row r="5">
@@ -577,28 +577,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.8882</v>
+        <v>-3.8596</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.5816</v>
+        <v>-5.5514</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1947</v>
+        <v>-2.1678</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8632</v>
+        <v>0.8623</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.5043</v>
+        <v>-4.4757</v>
       </c>
       <c r="G5" t="n">
-        <v>7e-06</v>
+        <v>8e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0158</v>
+        <v>0.0156</v>
       </c>
       <c r="I5" t="n">
-        <v>0.015</v>
+        <v>0.0148</v>
       </c>
     </row>
     <row r="6">
@@ -608,28 +608,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.5748</v>
+        <v>-1.3831</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.2797</v>
+        <v>-3.0865</v>
       </c>
       <c r="D6" t="n">
-        <v>0.13</v>
+        <v>0.3203</v>
       </c>
       <c r="E6" t="n">
-        <v>0.869</v>
+        <v>0.8683</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8123</v>
+        <v>-1.5929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07018000000000001</v>
+        <v>0.111425</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0026</v>
+        <v>0.002</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0018</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="7">
@@ -639,28 +639,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1323</v>
+        <v>3.1567</v>
       </c>
       <c r="C7" t="n">
-        <v>1.434</v>
+        <v>1.4605</v>
       </c>
       <c r="D7" t="n">
-        <v>4.8305</v>
+        <v>4.8529</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8656</v>
+        <v>0.8646</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6185</v>
+        <v>3.6511</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000308</v>
+        <v>0.000272</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0103</v>
+        <v>0.0104</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0095</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.3935</v>
+        <v>7.2371</v>
       </c>
       <c r="C8" t="n">
-        <v>5.736</v>
+        <v>5.5793</v>
       </c>
       <c r="D8" t="n">
-        <v>9.051</v>
+        <v>8.8949</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8449</v>
+        <v>0.845</v>
       </c>
       <c r="F8" t="n">
-        <v>8.750999999999999</v>
+        <v>8.564399999999999</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0572</v>
+        <v>0.0547</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0564</v>
+        <v>0.054</v>
       </c>
     </row>
     <row r="9">
@@ -722,17 +722,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>F=1.68</t>
+          <t>F=1.667</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.003585</v>
+        <v>0.004076</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0584</v>
+        <v>0.0578</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0237</v>
+        <v>0.0231</v>
       </c>
     </row>
   </sheetData>
@@ -793,19 +793,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.0565</v>
+        <v>94.12649999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>54.0572</v>
+        <v>54.0785</v>
       </c>
       <c r="D2" t="n">
-        <v>134.0559</v>
+        <v>134.1745</v>
       </c>
       <c r="E2" t="n">
-        <v>20.3878</v>
+        <v>20.4127</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6134</v>
+        <v>4.6112</v>
       </c>
       <c r="G2" t="n">
         <v>4e-06</v>
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.0604</v>
+        <v>42.192</v>
       </c>
       <c r="C3" t="n">
-        <v>39.692</v>
+        <v>39.8239</v>
       </c>
       <c r="D3" t="n">
-        <v>44.4287</v>
+        <v>44.56</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2072</v>
+        <v>1.207</v>
       </c>
       <c r="F3" t="n">
-        <v>34.8422</v>
+        <v>34.9556</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -843,19 +843,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.6031</v>
+        <v>-4.5142</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.7954</v>
+        <v>-5.7087</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.4107</v>
+        <v>-3.3197</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6077</v>
+        <v>0.6089</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.574</v>
+        <v>-7.4141</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -868,22 +868,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-12.6516</v>
+        <v>-12.6013</v>
       </c>
       <c r="C5" t="n">
-        <v>-22.2665</v>
+        <v>-22.2208</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.0368</v>
+        <v>-2.9818</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9007</v>
+        <v>4.9031</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5816</v>
+        <v>-2.5701</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009951</v>
+        <v>0.010286</v>
       </c>
     </row>
     <row r="6">
@@ -893,22 +893,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.6768</v>
+        <v>-3.7089</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.6132</v>
+        <v>-5.6493</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7404</v>
+        <v>-1.7684</v>
       </c>
       <c r="E6" t="n">
-        <v>0.987</v>
+        <v>0.9891</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7253</v>
+        <v>-3.7499</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000204</v>
+        <v>0.000185</v>
       </c>
     </row>
     <row r="7">
@@ -918,22 +918,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.3528</v>
+        <v>1.4432</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0585</v>
+        <v>0.0262</v>
       </c>
       <c r="D7" t="n">
-        <v>2.764</v>
+        <v>2.8603</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7193000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8807</v>
+        <v>1.9981</v>
       </c>
       <c r="G7" t="n">
-        <v>0.060258</v>
+        <v>0.045923</v>
       </c>
     </row>
     <row r="8">
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4559</v>
+        <v>0.48</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8545</v>
+        <v>-0.8299</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7664</v>
+        <v>1.79</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6679</v>
+        <v>0.6677</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6826</v>
+        <v>0.719</v>
       </c>
       <c r="G8" t="n">
-        <v>0.494981</v>
+        <v>0.472299</v>
       </c>
     </row>
     <row r="9">
@@ -968,22 +968,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.0328</v>
+        <v>18.9283</v>
       </c>
       <c r="C9" t="n">
-        <v>9.6714</v>
+        <v>9.5671</v>
       </c>
       <c r="D9" t="n">
-        <v>28.3942</v>
+        <v>28.2895</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7715</v>
+        <v>4.7714</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9888</v>
+        <v>3.967</v>
       </c>
       <c r="G9" t="n">
-        <v>6.999999999999999e-05</v>
+        <v>7.7e-05</v>
       </c>
     </row>
     <row r="10">
@@ -993,22 +993,22 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.1679</v>
+        <v>28.1479</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.889</v>
+        <v>-20.9689</v>
       </c>
       <c r="D10" t="n">
-        <v>77.22490000000001</v>
+        <v>77.2647</v>
       </c>
       <c r="E10" t="n">
-        <v>25.0045</v>
+        <v>25.0351</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1265</v>
+        <v>1.1243</v>
       </c>
       <c r="G10" t="n">
-        <v>0.260171</v>
+        <v>0.261092</v>
       </c>
     </row>
     <row r="11">
@@ -1018,22 +1018,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.3509</v>
+        <v>13.3623</v>
       </c>
       <c r="C11" t="n">
-        <v>-28.3212</v>
+        <v>-28.3607</v>
       </c>
       <c r="D11" t="n">
-        <v>55.023</v>
+        <v>55.0852</v>
       </c>
       <c r="E11" t="n">
-        <v>21.2404</v>
+        <v>21.2664</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6286</v>
+        <v>0.6283</v>
       </c>
       <c r="G11" t="n">
-        <v>0.529755</v>
+        <v>0.529908</v>
       </c>
     </row>
     <row r="12">
@@ -1043,22 +1043,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.3304</v>
+        <v>24.3676</v>
       </c>
       <c r="C12" t="n">
-        <v>-32.2852</v>
+        <v>-32.317</v>
       </c>
       <c r="D12" t="n">
-        <v>80.946</v>
+        <v>81.0522</v>
       </c>
       <c r="E12" t="n">
-        <v>28.8572</v>
+        <v>28.8925</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8431</v>
+        <v>0.8434</v>
       </c>
       <c r="G12" t="n">
-        <v>0.399321</v>
+        <v>0.399177</v>
       </c>
     </row>
     <row r="13">
@@ -1068,22 +1068,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.4072</v>
+        <v>26.3056</v>
       </c>
       <c r="C13" t="n">
-        <v>-15.2313</v>
+        <v>-15.3837</v>
       </c>
       <c r="D13" t="n">
-        <v>68.0457</v>
+        <v>67.9949</v>
       </c>
       <c r="E13" t="n">
-        <v>21.2233</v>
+        <v>21.2493</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2443</v>
+        <v>1.238</v>
       </c>
       <c r="G13" t="n">
-        <v>0.213646</v>
+        <v>0.215973</v>
       </c>
     </row>
     <row r="14">
@@ -1093,22 +1093,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.5463</v>
+        <v>14.3895</v>
       </c>
       <c r="C14" t="n">
-        <v>-28.6789</v>
+        <v>-28.8884</v>
       </c>
       <c r="D14" t="n">
-        <v>57.7714</v>
+        <v>57.6673</v>
       </c>
       <c r="E14" t="n">
-        <v>22.032</v>
+        <v>22.059</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6602</v>
+        <v>0.6523</v>
       </c>
       <c r="G14" t="n">
-        <v>0.50923</v>
+        <v>0.514319</v>
       </c>
     </row>
     <row r="15">
@@ -1118,22 +1118,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.9587</v>
+        <v>32.7782</v>
       </c>
       <c r="C15" t="n">
-        <v>-16.1999</v>
+        <v>-16.4393</v>
       </c>
       <c r="D15" t="n">
-        <v>82.1173</v>
+        <v>81.9956</v>
       </c>
       <c r="E15" t="n">
-        <v>25.0563</v>
+        <v>25.0864</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3154</v>
+        <v>1.3066</v>
       </c>
       <c r="G15" t="n">
-        <v>0.18863</v>
+        <v>0.191592</v>
       </c>
     </row>
     <row r="16">
@@ -1143,22 +1143,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13.6122</v>
+        <v>13.5632</v>
       </c>
       <c r="C16" t="n">
-        <v>-42.9758</v>
+        <v>-43.094</v>
       </c>
       <c r="D16" t="n">
-        <v>70.2002</v>
+        <v>70.2204</v>
       </c>
       <c r="E16" t="n">
-        <v>28.8431</v>
+        <v>28.8785</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4719</v>
+        <v>0.4697</v>
       </c>
       <c r="G16" t="n">
-        <v>0.637055</v>
+        <v>0.63868</v>
       </c>
     </row>
     <row r="17">
@@ -1168,22 +1168,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8.6311</v>
+        <v>8.5543</v>
       </c>
       <c r="C17" t="n">
-        <v>-32.9467</v>
+        <v>-33.0742</v>
       </c>
       <c r="D17" t="n">
-        <v>50.2089</v>
+        <v>50.1827</v>
       </c>
       <c r="E17" t="n">
-        <v>21.1924</v>
+        <v>21.2183</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4073</v>
+        <v>0.4032</v>
       </c>
       <c r="G17" t="n">
-        <v>0.683879</v>
+        <v>0.686905</v>
       </c>
     </row>
     <row r="18">
@@ -1193,22 +1193,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.8979</v>
+        <v>31.8999</v>
       </c>
       <c r="C18" t="n">
-        <v>-17.1764</v>
+        <v>-17.2343</v>
       </c>
       <c r="D18" t="n">
-        <v>80.9722</v>
+        <v>81.0341</v>
       </c>
       <c r="E18" t="n">
-        <v>25.0134</v>
+        <v>25.044</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2752</v>
+        <v>1.2738</v>
       </c>
       <c r="G18" t="n">
-        <v>0.202471</v>
+        <v>0.202994</v>
       </c>
     </row>
     <row r="19">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.1131</v>
+        <v>17.1177</v>
       </c>
       <c r="C19" t="n">
-        <v>-39.4854</v>
+        <v>-39.5498</v>
       </c>
       <c r="D19" t="n">
-        <v>73.7116</v>
+        <v>73.78530000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>28.8485</v>
+        <v>28.8837</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5926</v>
       </c>
       <c r="G19" t="n">
-        <v>0.553153</v>
+        <v>0.55353</v>
       </c>
     </row>
     <row r="20">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.9447</v>
+        <v>9.361000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>-27.0064</v>
+        <v>-31.4937</v>
       </c>
       <c r="D20" t="n">
-        <v>54.8959</v>
+        <v>50.2158</v>
       </c>
       <c r="E20" t="n">
-        <v>20.873</v>
+        <v>20.8239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6681</v>
+        <v>0.4495</v>
       </c>
       <c r="G20" t="n">
-        <v>0.504212</v>
+        <v>0.653127</v>
       </c>
     </row>
     <row r="21">
@@ -1268,22 +1268,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-20.3696</v>
+        <v>-20.821</v>
       </c>
       <c r="C21" t="n">
-        <v>-77.03570000000001</v>
+        <v>-77.5552</v>
       </c>
       <c r="D21" t="n">
-        <v>36.2965</v>
+        <v>35.9132</v>
       </c>
       <c r="E21" t="n">
-        <v>28.8829</v>
+        <v>28.9177</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7052</v>
+        <v>-0.72</v>
       </c>
       <c r="G21" t="n">
-        <v>0.480792</v>
+        <v>0.471659</v>
       </c>
     </row>
     <row r="22">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.5279</v>
+        <v>19.0619</v>
       </c>
       <c r="C22" t="n">
-        <v>-37.2459</v>
+        <v>-37.7798</v>
       </c>
       <c r="D22" t="n">
-        <v>76.3018</v>
+        <v>75.9036</v>
       </c>
       <c r="E22" t="n">
-        <v>28.9379</v>
+        <v>28.9725</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6748</v>
+        <v>0.6579</v>
       </c>
       <c r="G22" t="n">
-        <v>0.499917</v>
+        <v>0.510707</v>
       </c>
     </row>
     <row r="23">
@@ -1318,22 +1318,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34.6706</v>
+        <v>34.5403</v>
       </c>
       <c r="C23" t="n">
-        <v>-22.0236</v>
+        <v>-22.2231</v>
       </c>
       <c r="D23" t="n">
-        <v>91.3648</v>
+        <v>91.30370000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>28.8973</v>
+        <v>28.9326</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1998</v>
+        <v>1.1938</v>
       </c>
       <c r="G23" t="n">
-        <v>0.230455</v>
+        <v>0.232782</v>
       </c>
     </row>
     <row r="24">
@@ -1343,22 +1343,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68.2469</v>
+        <v>68.6247</v>
       </c>
       <c r="C24" t="n">
-        <v>11.3802</v>
+        <v>11.69</v>
       </c>
       <c r="D24" t="n">
-        <v>125.1136</v>
+        <v>125.5593</v>
       </c>
       <c r="E24" t="n">
-        <v>28.9852</v>
+        <v>29.0199</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3545</v>
+        <v>2.3647</v>
       </c>
       <c r="G24" t="n">
-        <v>0.018704</v>
+        <v>0.018199</v>
       </c>
     </row>
     <row r="25">
@@ -1368,22 +1368,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.7059</v>
+        <v>14.7108</v>
       </c>
       <c r="C25" t="n">
-        <v>-28.5932</v>
+        <v>-28.6409</v>
       </c>
       <c r="D25" t="n">
-        <v>58.0051</v>
+        <v>58.0626</v>
       </c>
       <c r="E25" t="n">
-        <v>22.0697</v>
+        <v>22.0966</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6663</v>
+        <v>0.6657</v>
       </c>
       <c r="G25" t="n">
-        <v>0.505321</v>
+        <v>0.505697</v>
       </c>
     </row>
     <row r="26">
@@ -1393,22 +1393,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-14.5181</v>
+        <v>-14.5969</v>
       </c>
       <c r="C26" t="n">
-        <v>-60.8016</v>
+        <v>-60.9365</v>
       </c>
       <c r="D26" t="n">
-        <v>31.7655</v>
+        <v>31.7428</v>
       </c>
       <c r="E26" t="n">
-        <v>23.5909</v>
+        <v>23.6196</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.618</v>
       </c>
       <c r="G26" t="n">
-        <v>0.538399</v>
+        <v>0.5366919999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1418,22 +1418,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.0426</v>
+        <v>7.0418</v>
       </c>
       <c r="C27" t="n">
-        <v>-39.1961</v>
+        <v>-39.253</v>
       </c>
       <c r="D27" t="n">
-        <v>53.2813</v>
+        <v>53.3366</v>
       </c>
       <c r="E27" t="n">
-        <v>23.5681</v>
+        <v>23.5967</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2988</v>
+        <v>0.2984</v>
       </c>
       <c r="G27" t="n">
-        <v>0.765128</v>
+        <v>0.765431</v>
       </c>
     </row>
     <row r="28">
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7.7202</v>
+        <v>7.6027</v>
       </c>
       <c r="C28" t="n">
-        <v>-35.0746</v>
+        <v>-35.2442</v>
       </c>
       <c r="D28" t="n">
-        <v>50.515</v>
+        <v>50.4496</v>
       </c>
       <c r="E28" t="n">
-        <v>21.8127</v>
+        <v>21.8393</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3539</v>
+        <v>0.3481</v>
       </c>
       <c r="G28" t="n">
-        <v>0.723453</v>
+        <v>0.72781</v>
       </c>
     </row>
     <row r="29">
@@ -1468,22 +1468,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1185</v>
+        <v>-0.0868</v>
       </c>
       <c r="C29" t="n">
-        <v>-40.5521</v>
+        <v>-40.5699</v>
       </c>
       <c r="D29" t="n">
-        <v>40.3151</v>
+        <v>40.3963</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6092</v>
+        <v>20.6345</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0057</v>
+        <v>-0.0042</v>
       </c>
       <c r="G29" t="n">
-        <v>0.995413</v>
+        <v>0.996645</v>
       </c>
     </row>
     <row r="30">
@@ -1493,22 +1493,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6.0456</v>
+        <v>6.0847</v>
       </c>
       <c r="C30" t="n">
-        <v>-50.5767</v>
+        <v>-50.6069</v>
       </c>
       <c r="D30" t="n">
-        <v>62.6678</v>
+        <v>62.7762</v>
       </c>
       <c r="E30" t="n">
-        <v>28.8606</v>
+        <v>28.896</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2095</v>
+        <v>0.2106</v>
       </c>
       <c r="G30" t="n">
-        <v>0.834113</v>
+        <v>0.833256</v>
       </c>
     </row>
     <row r="31">
@@ -1518,22 +1518,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>14.0481</v>
+        <v>13.8652</v>
       </c>
       <c r="C31" t="n">
-        <v>-29.7253</v>
+        <v>-29.9614</v>
       </c>
       <c r="D31" t="n">
-        <v>57.8216</v>
+        <v>57.6917</v>
       </c>
       <c r="E31" t="n">
-        <v>22.3115</v>
+        <v>22.3387</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6296</v>
+        <v>0.6207</v>
       </c>
       <c r="G31" t="n">
-        <v>0.529051</v>
+        <v>0.534926</v>
       </c>
     </row>
     <row r="32">
@@ -1543,22 +1543,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.8961</v>
+        <v>4.7834</v>
       </c>
       <c r="C32" t="n">
-        <v>-36.1407</v>
+        <v>-36.3034</v>
       </c>
       <c r="D32" t="n">
-        <v>45.933</v>
+        <v>45.8701</v>
       </c>
       <c r="E32" t="n">
-        <v>20.9166</v>
+        <v>20.9421</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2341</v>
+        <v>0.2284</v>
       </c>
       <c r="G32" t="n">
-        <v>0.814964</v>
+        <v>0.819367</v>
       </c>
     </row>
     <row r="33">
@@ -1568,22 +1568,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.5822</v>
+        <v>-2.6219</v>
       </c>
       <c r="C33" t="n">
-        <v>-42.8809</v>
+        <v>-42.9697</v>
       </c>
       <c r="D33" t="n">
-        <v>37.7165</v>
+        <v>37.726</v>
       </c>
       <c r="E33" t="n">
-        <v>20.5404</v>
+        <v>20.5655</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1257</v>
+        <v>-0.1275</v>
       </c>
       <c r="G33" t="n">
-        <v>0.89998</v>
+        <v>0.898575</v>
       </c>
     </row>
     <row r="34">
@@ -1593,22 +1593,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-27.5225</v>
+        <v>-27.7792</v>
       </c>
       <c r="C34" t="n">
-        <v>-84.1765</v>
+        <v>-84.5017</v>
       </c>
       <c r="D34" t="n">
-        <v>29.1314</v>
+        <v>28.9433</v>
       </c>
       <c r="E34" t="n">
-        <v>28.8768</v>
+        <v>28.9118</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9530999999999999</v>
+        <v>-0.9608</v>
       </c>
       <c r="G34" t="n">
-        <v>0.340728</v>
+        <v>0.336831</v>
       </c>
     </row>
     <row r="35">
@@ -1618,22 +1618,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9.8079</v>
+        <v>9.6632</v>
       </c>
       <c r="C35" t="n">
-        <v>-46.787</v>
+        <v>-47.0009</v>
       </c>
       <c r="D35" t="n">
-        <v>66.4028</v>
+        <v>66.3272</v>
       </c>
       <c r="E35" t="n">
-        <v>28.8466</v>
+        <v>28.882</v>
       </c>
       <c r="F35" t="n">
-        <v>0.34</v>
+        <v>0.3346</v>
       </c>
       <c r="G35" t="n">
-        <v>0.733915</v>
+        <v>0.738004</v>
       </c>
     </row>
     <row r="36">
@@ -1643,22 +1643,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12.11</v>
+        <v>12.1002</v>
       </c>
       <c r="C36" t="n">
-        <v>-37.0349</v>
+        <v>-37.1034</v>
       </c>
       <c r="D36" t="n">
-        <v>61.2548</v>
+        <v>61.3039</v>
       </c>
       <c r="E36" t="n">
-        <v>25.0493</v>
+        <v>25.0794</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4834</v>
+        <v>0.4825</v>
       </c>
       <c r="G36" t="n">
-        <v>0.628868</v>
+        <v>0.6295539999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1668,22 +1668,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.7004</v>
+        <v>17.8559</v>
       </c>
       <c r="C37" t="n">
-        <v>-31.4733</v>
+        <v>-31.3776</v>
       </c>
       <c r="D37" t="n">
-        <v>66.8741</v>
+        <v>67.0894</v>
       </c>
       <c r="E37" t="n">
-        <v>25.064</v>
+        <v>25.0946</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7062</v>
+        <v>0.7115</v>
       </c>
       <c r="G37" t="n">
-        <v>0.480196</v>
+        <v>0.476885</v>
       </c>
     </row>
     <row r="38">
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9.9321</v>
+        <v>9.8218</v>
       </c>
       <c r="C38" t="n">
-        <v>-30.2237</v>
+        <v>-30.3824</v>
       </c>
       <c r="D38" t="n">
-        <v>50.0878</v>
+        <v>50.0261</v>
       </c>
       <c r="E38" t="n">
-        <v>20.4676</v>
+        <v>20.4923</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4853</v>
+        <v>0.4793</v>
       </c>
       <c r="G38" t="n">
-        <v>0.62758</v>
+        <v>0.631817</v>
       </c>
     </row>
     <row r="39">
@@ -1718,22 +1718,22 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.7918</v>
+        <v>17.656</v>
       </c>
       <c r="C39" t="n">
-        <v>-26.1272</v>
+        <v>-26.316</v>
       </c>
       <c r="D39" t="n">
-        <v>61.7107</v>
+        <v>61.628</v>
       </c>
       <c r="E39" t="n">
-        <v>22.3856</v>
+        <v>22.4128</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7948</v>
+        <v>0.7877999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>0.426895</v>
+        <v>0.430988</v>
       </c>
     </row>
     <row r="40">
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13.404</v>
+        <v>13.2764</v>
       </c>
       <c r="C40" t="n">
-        <v>-26.7026</v>
+        <v>-26.8789</v>
       </c>
       <c r="D40" t="n">
-        <v>53.5107</v>
+        <v>53.4317</v>
       </c>
       <c r="E40" t="n">
-        <v>20.4425</v>
+        <v>20.4674</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>0.512146</v>
+        <v>0.51668</v>
       </c>
     </row>
     <row r="41">
@@ -1768,22 +1768,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.4174</v>
+        <v>26.4251</v>
       </c>
       <c r="C41" t="n">
-        <v>-30.1334</v>
+        <v>-30.1949</v>
       </c>
       <c r="D41" t="n">
-        <v>82.9682</v>
+        <v>83.04510000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>28.8242</v>
+        <v>28.8595</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9165</v>
+        <v>0.9156</v>
       </c>
       <c r="G41" t="n">
-        <v>0.359586</v>
+        <v>0.360034</v>
       </c>
     </row>
     <row r="42">
@@ -1793,22 +1793,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.3823</v>
+        <v>34.3898</v>
       </c>
       <c r="C42" t="n">
-        <v>-22.2421</v>
+        <v>-22.3038</v>
       </c>
       <c r="D42" t="n">
-        <v>91.0067</v>
+        <v>91.0834</v>
       </c>
       <c r="E42" t="n">
-        <v>28.8617</v>
+        <v>28.897</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1913</v>
+        <v>1.1901</v>
       </c>
       <c r="G42" t="n">
-        <v>0.233777</v>
+        <v>0.234247</v>
       </c>
     </row>
     <row r="43">
@@ -1818,22 +1818,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.5364</v>
+        <v>18.3999</v>
       </c>
       <c r="C43" t="n">
-        <v>-21.6069</v>
+        <v>-21.7922</v>
       </c>
       <c r="D43" t="n">
-        <v>58.6797</v>
+        <v>58.592</v>
       </c>
       <c r="E43" t="n">
-        <v>20.4612</v>
+        <v>20.4861</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9059</v>
+        <v>0.8982</v>
       </c>
       <c r="G43" t="n">
-        <v>0.365153</v>
+        <v>0.369277</v>
       </c>
     </row>
     <row r="44">
@@ -1843,22 +1843,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10.4689</v>
+        <v>10.378</v>
       </c>
       <c r="C44" t="n">
-        <v>-32.3001</v>
+        <v>-32.4432</v>
       </c>
       <c r="D44" t="n">
-        <v>53.2379</v>
+        <v>53.1993</v>
       </c>
       <c r="E44" t="n">
-        <v>21.7995</v>
+        <v>21.8262</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4802</v>
+        <v>0.4755</v>
       </c>
       <c r="G44" t="n">
-        <v>0.631148</v>
+        <v>0.634527</v>
       </c>
     </row>
     <row r="45">
@@ -1868,22 +1868,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.1939</v>
+        <v>16.0454</v>
       </c>
       <c r="C45" t="n">
-        <v>-30.0131</v>
+        <v>-30.218</v>
       </c>
       <c r="D45" t="n">
-        <v>62.4008</v>
+        <v>62.3087</v>
       </c>
       <c r="E45" t="n">
-        <v>23.5519</v>
+        <v>23.5807</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6876</v>
+        <v>0.6804</v>
       </c>
       <c r="G45" t="n">
-        <v>0.491846</v>
+        <v>0.496352</v>
       </c>
     </row>
     <row r="46">
@@ -1893,22 +1893,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-4.1877</v>
+        <v>-4.5583</v>
       </c>
       <c r="C46" t="n">
-        <v>-61.1032</v>
+        <v>-61.5422</v>
       </c>
       <c r="D46" t="n">
-        <v>52.7277</v>
+        <v>52.4256</v>
       </c>
       <c r="E46" t="n">
-        <v>29.01</v>
+        <v>29.045</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1444</v>
+        <v>-0.1569</v>
       </c>
       <c r="G46" t="n">
-        <v>0.885244</v>
+        <v>0.875318</v>
       </c>
     </row>
     <row r="47">
@@ -1918,22 +1918,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25.0103</v>
+        <v>24.9213</v>
       </c>
       <c r="C47" t="n">
-        <v>-31.5753</v>
+        <v>-31.7336</v>
       </c>
       <c r="D47" t="n">
-        <v>81.5959</v>
+        <v>81.5761</v>
       </c>
       <c r="E47" t="n">
-        <v>28.8419</v>
+        <v>28.8773</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8672</v>
+        <v>0.863</v>
       </c>
       <c r="G47" t="n">
-        <v>0.386031</v>
+        <v>0.388305</v>
       </c>
     </row>
     <row r="48">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>42.1122</v>
+        <v>42.1787</v>
       </c>
       <c r="C48" t="n">
-        <v>-14.4521</v>
+        <v>-14.4548</v>
       </c>
       <c r="D48" t="n">
-        <v>98.6765</v>
+        <v>98.8121</v>
       </c>
       <c r="E48" t="n">
-        <v>28.831</v>
+        <v>28.8664</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4607</v>
+        <v>1.4612</v>
       </c>
       <c r="G48" t="n">
-        <v>0.144369</v>
+        <v>0.144228</v>
       </c>
     </row>
     <row r="49">
@@ -1968,22 +1968,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.3938</v>
+        <v>5.3685</v>
       </c>
       <c r="C49" t="n">
-        <v>-34.9556</v>
+        <v>-35.0302</v>
       </c>
       <c r="D49" t="n">
-        <v>45.7431</v>
+        <v>45.7673</v>
       </c>
       <c r="E49" t="n">
-        <v>20.5662</v>
+        <v>20.5915</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2623</v>
+        <v>0.2607</v>
       </c>
       <c r="G49" t="n">
-        <v>0.793163</v>
+        <v>0.794356</v>
       </c>
     </row>
     <row r="50">
@@ -1993,22 +1993,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.0033</v>
+        <v>26.8656</v>
       </c>
       <c r="C50" t="n">
-        <v>-16.9372</v>
+        <v>-17.1282</v>
       </c>
       <c r="D50" t="n">
-        <v>70.94370000000001</v>
+        <v>70.8593</v>
       </c>
       <c r="E50" t="n">
-        <v>22.3966</v>
+        <v>22.4239</v>
       </c>
       <c r="F50" t="n">
-        <v>1.2057</v>
+        <v>1.1981</v>
       </c>
       <c r="G50" t="n">
-        <v>0.228175</v>
+        <v>0.23112</v>
       </c>
     </row>
     <row r="51">
@@ -2018,22 +2018,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2857</v>
+        <v>-0.2108</v>
       </c>
       <c r="C51" t="n">
-        <v>-56.9127</v>
+        <v>-56.907</v>
       </c>
       <c r="D51" t="n">
-        <v>56.3412</v>
+        <v>56.4853</v>
       </c>
       <c r="E51" t="n">
-        <v>28.863</v>
+        <v>28.8983</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.0073</v>
       </c>
       <c r="G51" t="n">
-        <v>0.992104</v>
+        <v>0.99418</v>
       </c>
     </row>
     <row r="52">
@@ -2043,22 +2043,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.6443</v>
+        <v>3.5152</v>
       </c>
       <c r="C52" t="n">
-        <v>-53.1504</v>
+        <v>-53.3487</v>
       </c>
       <c r="D52" t="n">
-        <v>60.4389</v>
+        <v>60.3792</v>
       </c>
       <c r="E52" t="n">
-        <v>28.9485</v>
+        <v>28.9839</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1259</v>
+        <v>0.1213</v>
       </c>
       <c r="G52" t="n">
-        <v>0.899841</v>
+        <v>0.903488</v>
       </c>
     </row>
     <row r="53">
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10.2599</v>
+        <v>10.1524</v>
       </c>
       <c r="C53" t="n">
-        <v>-29.8333</v>
+        <v>-29.9896</v>
       </c>
       <c r="D53" t="n">
-        <v>50.353</v>
+        <v>50.2943</v>
       </c>
       <c r="E53" t="n">
-        <v>20.4357</v>
+        <v>20.4606</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5021</v>
+        <v>0.4962</v>
       </c>
       <c r="G53" t="n">
-        <v>0.615719</v>
+        <v>0.619849</v>
       </c>
     </row>
     <row r="54">
@@ -2093,22 +2093,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-30.0625</v>
+        <v>-29.9678</v>
       </c>
       <c r="C54" t="n">
-        <v>-86.7127</v>
+        <v>-86.6871</v>
       </c>
       <c r="D54" t="n">
-        <v>26.5877</v>
+        <v>26.7515</v>
       </c>
       <c r="E54" t="n">
-        <v>28.8748</v>
+        <v>28.9102</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.0411</v>
+        <v>-1.0366</v>
       </c>
       <c r="G54" t="n">
-        <v>0.298023</v>
+        <v>0.300135</v>
       </c>
     </row>
   </sheetData>
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1265</v>
+        <v>1269</v>
       </c>
       <c r="C2" t="inlineStr"/>
     </row>
@@ -2160,7 +2160,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.584</v>
+        <v>0.5833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5661</v>
+        <v>0.5654</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.7138</v>
+        <v>32.7277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11268.24</v>
+        <v>11306.82</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11540.81</v>
+        <v>11579.56</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.9457</v>
+        <v>19.9716</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.6597</v>
+        <v>14.676</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.498</v>
+        <v>0.5444</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0689</v>
+        <v>0.0417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9691</v>
+        <v>0.9668</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>98.1503</v>
+        <v>98.8788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.000115</v>
+        <v>9.6e-05</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9552</v>
+        <v>1.96</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>366.96</v>
+        <v>367.8</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/연구코드/aec/results/신촌/linear_results.xlsx
+++ b/연구코드/aec/results/신촌/linear_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,28 +484,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.5908</v>
+        <v>43.6693</v>
       </c>
       <c r="C2" t="n">
-        <v>41.1706</v>
+        <v>41.2733</v>
       </c>
       <c r="D2" t="n">
-        <v>46.0111</v>
+        <v>46.0653</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2337</v>
+        <v>1.2213</v>
       </c>
       <c r="F2" t="n">
-        <v>35.3347</v>
+        <v>35.7566</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4963</v>
+        <v>0.5023</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4959</v>
+        <v>0.5019</v>
       </c>
     </row>
     <row r="3">
@@ -515,59 +515,59 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-2.3588</v>
+        <v>-2.3078</v>
       </c>
       <c r="C3" t="n">
-        <v>-4.0589</v>
+        <v>-4.0011</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.6586</v>
+        <v>-0.6145</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8666</v>
+        <v>0.8631</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.7219</v>
+        <v>-2.6738</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00658</v>
+        <v>0.007595</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0058</v>
+        <v>0.0056</v>
       </c>
       <c r="I3" t="n">
-        <v>0.005</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEC: p25 (표준화)</t>
+          <t>AEC: mean (표준화)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.5579</v>
+        <v>7.1988</v>
       </c>
       <c r="C4" t="n">
-        <v>5.9045</v>
+        <v>5.5478</v>
       </c>
       <c r="D4" t="n">
-        <v>9.211399999999999</v>
+        <v>8.8499</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8428</v>
+        <v>0.8416</v>
       </c>
       <c r="F4" t="n">
-        <v>8.967599999999999</v>
+        <v>8.553900000000001</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0597</v>
+        <v>0.0546</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0589</v>
+        <v>0.0539</v>
       </c>
     </row>
     <row r="5">
@@ -577,28 +577,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-3.8596</v>
+        <v>-3.874</v>
       </c>
       <c r="C5" t="n">
-        <v>-5.5514</v>
+        <v>-5.5585</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.1678</v>
+        <v>-2.1894</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8623</v>
+        <v>0.8587</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.4757</v>
+        <v>-4.5116</v>
       </c>
       <c r="G5" t="n">
-        <v>8e-06</v>
+        <v>7e-06</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0156</v>
+        <v>0.0158</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0148</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="6">
@@ -608,25 +608,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.3831</v>
+        <v>-1.3569</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.0865</v>
+        <v>-3.0534</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3203</v>
+        <v>0.3395</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8683</v>
+        <v>0.8647</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5929</v>
+        <v>-1.5693</v>
       </c>
       <c r="G6" t="n">
-        <v>0.111425</v>
+        <v>0.116835</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="I6" t="n">
         <v>0.0012</v>
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1567</v>
+        <v>3.1413</v>
       </c>
       <c r="C7" t="n">
-        <v>1.4605</v>
+        <v>1.4521</v>
       </c>
       <c r="D7" t="n">
-        <v>4.8529</v>
+        <v>4.8305</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8646</v>
+        <v>0.861</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6511</v>
+        <v>3.6483</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000272</v>
+        <v>0.000275</v>
       </c>
       <c r="H7" t="n">
         <v>0.0104</v>
@@ -666,73 +666,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AEC: mean (표준화)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>7.2371</v>
-      </c>
-      <c r="C8" t="n">
-        <v>5.5793</v>
-      </c>
-      <c r="D8" t="n">
-        <v>8.8949</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8.564399999999999</v>
+          <t>ManufacturerModelName (F-test)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>N/A (범주형)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>F=1.642</t>
+        </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.005194</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0547</v>
+        <v>0.057</v>
       </c>
       <c r="I8" t="n">
-        <v>0.054</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ManufacturerModelName (F-test)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>N/A (범주형)</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>F=1.667</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0.004076</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.0578</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.0231</v>
+        <v>0.0223</v>
       </c>
     </row>
   </sheetData>
@@ -746,7 +715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,19 +762,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>94.12649999999999</v>
+        <v>94.03</v>
       </c>
       <c r="C2" t="n">
-        <v>54.0785</v>
+        <v>54.276</v>
       </c>
       <c r="D2" t="n">
-        <v>134.1745</v>
+        <v>133.7839</v>
       </c>
       <c r="E2" t="n">
-        <v>20.4127</v>
+        <v>20.2628</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6112</v>
+        <v>4.6405</v>
       </c>
       <c r="G2" t="n">
         <v>4e-06</v>
@@ -818,19 +787,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.192</v>
+        <v>42.0461</v>
       </c>
       <c r="C3" t="n">
-        <v>39.8239</v>
+        <v>39.7033</v>
       </c>
       <c r="D3" t="n">
-        <v>44.56</v>
+        <v>44.3889</v>
       </c>
       <c r="E3" t="n">
-        <v>1.207</v>
+        <v>1.1941</v>
       </c>
       <c r="F3" t="n">
-        <v>34.9556</v>
+        <v>35.2104</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -843,19 +812,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-4.5142</v>
+        <v>-4.49</v>
       </c>
       <c r="C4" t="n">
-        <v>-5.7087</v>
+        <v>-5.6756</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.3197</v>
+        <v>-3.3044</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6089</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.4141</v>
+        <v>-7.4299</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -864,26 +833,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>p25_z</t>
+          <t>mean_z</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-12.6013</v>
+        <v>6.7256</v>
       </c>
       <c r="C5" t="n">
-        <v>-22.2208</v>
+        <v>5.3879</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.9818</v>
+        <v>8.0634</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9031</v>
+        <v>0.6818</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5701</v>
+        <v>9.863899999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.010286</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -893,22 +862,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-3.7089</v>
+        <v>-1.8994</v>
       </c>
       <c r="C6" t="n">
-        <v>-5.6493</v>
+        <v>-3.2401</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.7684</v>
+        <v>-0.5587</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9891</v>
+        <v>0.6834</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.7499</v>
+        <v>-2.7796</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000185</v>
+        <v>0.005527</v>
       </c>
     </row>
     <row r="7">
@@ -918,22 +887,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.4432</v>
+        <v>2.0131</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0262</v>
+        <v>0.6623</v>
       </c>
       <c r="D7" t="n">
-        <v>2.8603</v>
+        <v>3.3639</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.6885</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9981</v>
+        <v>2.9238</v>
       </c>
       <c r="G7" t="n">
-        <v>0.045923</v>
+        <v>0.003521</v>
       </c>
     </row>
     <row r="8">
@@ -943,1172 +912,1147 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.48</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.8299</v>
+        <v>-0.6263</v>
       </c>
       <c r="D8" t="n">
-        <v>1.79</v>
+        <v>1.9599</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6677</v>
+        <v>0.6591</v>
       </c>
       <c r="F8" t="n">
-        <v>0.719</v>
+        <v>1.0117</v>
       </c>
       <c r="G8" t="n">
-        <v>0.472299</v>
+        <v>0.311867</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mean_z</t>
+          <t>Model_Alexion</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18.9283</v>
+        <v>27.5908</v>
       </c>
       <c r="C9" t="n">
-        <v>9.5671</v>
+        <v>-21.1642</v>
       </c>
       <c r="D9" t="n">
-        <v>28.2895</v>
+        <v>76.3458</v>
       </c>
       <c r="E9" t="n">
-        <v>4.7714</v>
+        <v>24.8507</v>
       </c>
       <c r="F9" t="n">
-        <v>3.967</v>
+        <v>1.1103</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7e-05</v>
+        <v>0.267106</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Model_Alexion</t>
+          <t>Model_Aquilion</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.1479</v>
+        <v>12.5233</v>
       </c>
       <c r="C10" t="n">
-        <v>-20.9689</v>
+        <v>-28.889</v>
       </c>
       <c r="D10" t="n">
-        <v>77.2647</v>
+        <v>53.9355</v>
       </c>
       <c r="E10" t="n">
-        <v>25.0351</v>
+        <v>21.1081</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1243</v>
+        <v>0.5933</v>
       </c>
       <c r="G10" t="n">
-        <v>0.261092</v>
+        <v>0.553096</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Model_Aquilion</t>
+          <t>Model_Aquilion Lightning</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.3623</v>
+        <v>24.2238</v>
       </c>
       <c r="C11" t="n">
-        <v>-28.3607</v>
+        <v>-32.0447</v>
       </c>
       <c r="D11" t="n">
-        <v>55.0852</v>
+        <v>80.4923</v>
       </c>
       <c r="E11" t="n">
-        <v>21.2664</v>
+        <v>28.6804</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6283</v>
+        <v>0.8446</v>
       </c>
       <c r="G11" t="n">
-        <v>0.529908</v>
+        <v>0.398494</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Model_Aquilion Lightning</t>
+          <t>Model_Aquilion ONE</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.3676</v>
+        <v>25.8344</v>
       </c>
       <c r="C12" t="n">
-        <v>-32.317</v>
+        <v>-15.5479</v>
       </c>
       <c r="D12" t="n">
-        <v>81.0522</v>
+        <v>67.2166</v>
       </c>
       <c r="E12" t="n">
-        <v>28.8925</v>
+        <v>21.0928</v>
       </c>
       <c r="F12" t="n">
-        <v>0.8434</v>
+        <v>1.2248</v>
       </c>
       <c r="G12" t="n">
-        <v>0.399177</v>
+        <v>0.220889</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Model_Aquilion ONE</t>
+          <t>Model_Aquilion PRIME</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26.3056</v>
+        <v>14.5272</v>
       </c>
       <c r="C13" t="n">
-        <v>-15.3837</v>
+        <v>-28.4326</v>
       </c>
       <c r="D13" t="n">
-        <v>67.9949</v>
+        <v>57.4869</v>
       </c>
       <c r="E13" t="n">
-        <v>21.2493</v>
+        <v>21.8968</v>
       </c>
       <c r="F13" t="n">
-        <v>1.238</v>
+        <v>0.6634</v>
       </c>
       <c r="G13" t="n">
-        <v>0.215973</v>
+        <v>0.507177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Model_Aquilion PRIME</t>
+          <t>Model_Aquilion/LB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.3895</v>
+        <v>34.3775</v>
       </c>
       <c r="C14" t="n">
-        <v>-28.8884</v>
+        <v>-14.4615</v>
       </c>
       <c r="D14" t="n">
-        <v>57.6673</v>
+        <v>83.21639999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>22.059</v>
+        <v>24.8935</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6523</v>
+        <v>1.381</v>
       </c>
       <c r="G14" t="n">
-        <v>0.514319</v>
+        <v>0.167538</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Model_Aquilion/LB</t>
+          <t>Model_Brilliance 40</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32.7782</v>
+        <v>14.2697</v>
       </c>
       <c r="C15" t="n">
-        <v>-16.4393</v>
+        <v>-41.9693</v>
       </c>
       <c r="D15" t="n">
-        <v>81.9956</v>
+        <v>70.5086</v>
       </c>
       <c r="E15" t="n">
-        <v>25.0864</v>
+        <v>28.6653</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3066</v>
+        <v>0.4978</v>
       </c>
       <c r="G15" t="n">
-        <v>0.191592</v>
+        <v>0.618713</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Model_Brilliance 40</t>
+          <t>Model_Brilliance 64</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13.5632</v>
+        <v>9.4223</v>
       </c>
       <c r="C16" t="n">
-        <v>-43.094</v>
+        <v>-31.895</v>
       </c>
       <c r="D16" t="n">
-        <v>70.2204</v>
+        <v>50.7397</v>
       </c>
       <c r="E16" t="n">
-        <v>28.8785</v>
+        <v>21.0597</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4697</v>
+        <v>0.4474</v>
       </c>
       <c r="G16" t="n">
-        <v>0.63868</v>
+        <v>0.654658</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Model_Brilliance 64</t>
+          <t>Model_Brivo CT385 Series</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8.5543</v>
+        <v>33.079</v>
       </c>
       <c r="C17" t="n">
-        <v>-33.0742</v>
+        <v>-15.6855</v>
       </c>
       <c r="D17" t="n">
-        <v>50.1827</v>
+        <v>81.8434</v>
       </c>
       <c r="E17" t="n">
-        <v>21.2183</v>
+        <v>24.8555</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4032</v>
+        <v>1.3308</v>
       </c>
       <c r="G17" t="n">
-        <v>0.686905</v>
+        <v>0.183488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Model_Brivo CT385 Series</t>
+          <t>Model_Definition Edge</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>31.8999</v>
+        <v>16.5814</v>
       </c>
       <c r="C18" t="n">
-        <v>-17.2343</v>
+        <v>-39.6689</v>
       </c>
       <c r="D18" t="n">
-        <v>81.0341</v>
+        <v>72.8318</v>
       </c>
       <c r="E18" t="n">
-        <v>25.044</v>
+        <v>28.6712</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2738</v>
+        <v>0.5783</v>
       </c>
       <c r="G18" t="n">
-        <v>0.202994</v>
+        <v>0.563147</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Model_Definition Edge</t>
+          <t>Model_Discovery CT750 HD</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17.1177</v>
+        <v>10.0977</v>
       </c>
       <c r="C19" t="n">
-        <v>-39.5498</v>
+        <v>-30.4539</v>
       </c>
       <c r="D19" t="n">
-        <v>73.78530000000001</v>
+        <v>50.6493</v>
       </c>
       <c r="E19" t="n">
-        <v>28.8837</v>
+        <v>20.6694</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5926</v>
+        <v>0.4885</v>
       </c>
       <c r="G19" t="n">
-        <v>0.55353</v>
+        <v>0.62526</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Model_Discovery CT750 HD</t>
+          <t>Model_ECLOS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9.361000000000001</v>
+        <v>-20.4539</v>
       </c>
       <c r="C20" t="n">
-        <v>-31.4937</v>
+        <v>-76.7693</v>
       </c>
       <c r="D20" t="n">
-        <v>50.2158</v>
+        <v>35.8616</v>
       </c>
       <c r="E20" t="n">
-        <v>20.8239</v>
+        <v>28.7043</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4495</v>
+        <v>-0.7126</v>
       </c>
       <c r="G20" t="n">
-        <v>0.653127</v>
+        <v>0.476248</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Model_ECLOS</t>
+          <t>Model_Emotion 16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-20.821</v>
+        <v>18.8171</v>
       </c>
       <c r="C21" t="n">
-        <v>-77.5552</v>
+        <v>-37.6073</v>
       </c>
       <c r="D21" t="n">
-        <v>35.9132</v>
+        <v>75.2415</v>
       </c>
       <c r="E21" t="n">
-        <v>28.9177</v>
+        <v>28.7599</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.72</v>
+        <v>0.6543</v>
       </c>
       <c r="G21" t="n">
-        <v>0.471659</v>
+        <v>0.513052</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Model_Emotion 16</t>
+          <t>Model_Emotion 16 (2007)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.0619</v>
+        <v>32.7538</v>
       </c>
       <c r="C22" t="n">
-        <v>-37.7798</v>
+        <v>-23.5794</v>
       </c>
       <c r="D22" t="n">
-        <v>75.9036</v>
+        <v>89.0869</v>
       </c>
       <c r="E22" t="n">
-        <v>28.9725</v>
+        <v>28.7133</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6579</v>
+        <v>1.1407</v>
       </c>
       <c r="G22" t="n">
-        <v>0.510707</v>
+        <v>0.254212</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Model_Emotion 16 (2007)</t>
+          <t>Model_GMS Revolution FT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34.5403</v>
+        <v>68.44199999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>-22.2231</v>
+        <v>11.9265</v>
       </c>
       <c r="D23" t="n">
-        <v>91.30370000000001</v>
+        <v>124.9575</v>
       </c>
       <c r="E23" t="n">
-        <v>28.9326</v>
+        <v>28.8063</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1938</v>
+        <v>2.3759</v>
       </c>
       <c r="G23" t="n">
-        <v>0.232782</v>
+        <v>0.017658</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Model_GMS Revolution FT</t>
+          <t>Model_Ingenuity CT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>68.6247</v>
+        <v>15.3553</v>
       </c>
       <c r="C24" t="n">
-        <v>11.69</v>
+        <v>-27.6753</v>
       </c>
       <c r="D24" t="n">
-        <v>125.5593</v>
+        <v>58.386</v>
       </c>
       <c r="E24" t="n">
-        <v>29.0199</v>
+        <v>21.933</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3647</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.018199</v>
+        <v>0.483997</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT</t>
+          <t>Model_Ingenuity CT Elite</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>14.7108</v>
+        <v>-13.4183</v>
       </c>
       <c r="C25" t="n">
-        <v>-28.6409</v>
+        <v>-59.4086</v>
       </c>
       <c r="D25" t="n">
-        <v>58.0626</v>
+        <v>32.5719</v>
       </c>
       <c r="E25" t="n">
-        <v>22.0966</v>
+        <v>23.4415</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6657</v>
+        <v>-0.5724</v>
       </c>
       <c r="G25" t="n">
-        <v>0.505697</v>
+        <v>0.567145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Model_Ingenuity CT Elite</t>
+          <t>Model_Ingenuity Core</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-14.5969</v>
+        <v>8.968400000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>-60.9365</v>
+        <v>-36.9629</v>
       </c>
       <c r="D26" t="n">
-        <v>31.7428</v>
+        <v>54.8996</v>
       </c>
       <c r="E26" t="n">
-        <v>23.6196</v>
+        <v>23.4114</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.618</v>
+        <v>0.3831</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5366919999999999</v>
+        <v>0.70173</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core</t>
+          <t>Model_Ingenuity Core 128</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.0418</v>
+        <v>7.7004</v>
       </c>
       <c r="C27" t="n">
-        <v>-39.253</v>
+        <v>-34.8319</v>
       </c>
       <c r="D27" t="n">
-        <v>53.3366</v>
+        <v>50.2326</v>
       </c>
       <c r="E27" t="n">
-        <v>23.5967</v>
+        <v>21.6789</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2984</v>
+        <v>0.3552</v>
       </c>
       <c r="G27" t="n">
-        <v>0.765431</v>
+        <v>0.7225009999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Model_Ingenuity Core 128</t>
+          <t>Model_LightSpeed VCT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7.6027</v>
+        <v>0.3824</v>
       </c>
       <c r="C28" t="n">
-        <v>-35.2442</v>
+        <v>-39.8022</v>
       </c>
       <c r="D28" t="n">
-        <v>50.4496</v>
+        <v>40.567</v>
       </c>
       <c r="E28" t="n">
-        <v>21.8393</v>
+        <v>20.4823</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3481</v>
+        <v>0.0187</v>
       </c>
       <c r="G28" t="n">
-        <v>0.72781</v>
+        <v>0.985108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Model_LightSpeed VCT</t>
+          <t>Model_MX 16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.0868</v>
+        <v>5.6805</v>
       </c>
       <c r="C29" t="n">
-        <v>-40.5699</v>
+        <v>-50.594</v>
       </c>
       <c r="D29" t="n">
-        <v>40.3963</v>
+        <v>61.9551</v>
       </c>
       <c r="E29" t="n">
-        <v>20.6345</v>
+        <v>28.6835</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0042</v>
+        <v>0.198</v>
       </c>
       <c r="G29" t="n">
-        <v>0.996645</v>
+        <v>0.843045</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Model_MX 16</t>
+          <t>Model_Optima CT660</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6.0847</v>
+        <v>13.7814</v>
       </c>
       <c r="C30" t="n">
-        <v>-50.6069</v>
+        <v>-29.7234</v>
       </c>
       <c r="D30" t="n">
-        <v>62.7762</v>
+        <v>57.2863</v>
       </c>
       <c r="E30" t="n">
-        <v>28.896</v>
+        <v>22.1747</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2106</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.833256</v>
+        <v>0.5343909999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Model_Optima CT660</t>
+          <t>Model_Revolution CT</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>13.8652</v>
+        <v>5.0597</v>
       </c>
       <c r="C31" t="n">
-        <v>-29.9614</v>
+        <v>-35.7245</v>
       </c>
       <c r="D31" t="n">
-        <v>57.6917</v>
+        <v>45.8439</v>
       </c>
       <c r="E31" t="n">
-        <v>22.3387</v>
+        <v>20.788</v>
       </c>
       <c r="F31" t="n">
-        <v>0.6207</v>
+        <v>0.2434</v>
       </c>
       <c r="G31" t="n">
-        <v>0.534926</v>
+        <v>0.807741</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Model_Revolution CT</t>
+          <t>Model_Revolution EVO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.7834</v>
+        <v>-1.5955</v>
       </c>
       <c r="C32" t="n">
-        <v>-36.3034</v>
+        <v>-41.6464</v>
       </c>
       <c r="D32" t="n">
-        <v>45.8701</v>
+        <v>38.4554</v>
       </c>
       <c r="E32" t="n">
-        <v>20.9421</v>
+        <v>20.4142</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2284</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0.819367</v>
+        <v>0.937716</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Model_Revolution EVO</t>
+          <t>Model_Revolution Frontier</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-2.6219</v>
+        <v>-27.9067</v>
       </c>
       <c r="C33" t="n">
-        <v>-42.9697</v>
+        <v>-84.2128</v>
       </c>
       <c r="D33" t="n">
-        <v>37.726</v>
+        <v>28.3994</v>
       </c>
       <c r="E33" t="n">
-        <v>20.5655</v>
+        <v>28.6996</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1275</v>
+        <v>-0.9724</v>
       </c>
       <c r="G33" t="n">
-        <v>0.898575</v>
+        <v>0.331058</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Model_Revolution Frontier</t>
+          <t>Model_Revolution HD</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-27.7792</v>
+        <v>10.1211</v>
       </c>
       <c r="C34" t="n">
-        <v>-84.5017</v>
+        <v>-46.1255</v>
       </c>
       <c r="D34" t="n">
-        <v>28.9433</v>
+        <v>66.3676</v>
       </c>
       <c r="E34" t="n">
-        <v>28.9118</v>
+        <v>28.6692</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9608</v>
+        <v>0.353</v>
       </c>
       <c r="G34" t="n">
-        <v>0.336831</v>
+        <v>0.724128</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Model_Revolution HD</t>
+          <t>Model_SOMATOM Definition</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>9.6632</v>
+        <v>14.8328</v>
       </c>
       <c r="C35" t="n">
-        <v>-47.0009</v>
+        <v>-33.9658</v>
       </c>
       <c r="D35" t="n">
-        <v>66.3272</v>
+        <v>63.6313</v>
       </c>
       <c r="E35" t="n">
-        <v>28.882</v>
+        <v>24.8729</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3346</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.738004</v>
+        <v>0.551057</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition</t>
+          <t>Model_SOMATOM Definition AS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12.1002</v>
+        <v>16.0145</v>
       </c>
       <c r="C36" t="n">
-        <v>-37.1034</v>
+        <v>-32.8355</v>
       </c>
       <c r="D36" t="n">
-        <v>61.3039</v>
+        <v>64.8644</v>
       </c>
       <c r="E36" t="n">
-        <v>25.0794</v>
+        <v>24.8991</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4825</v>
+        <v>0.6432</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6295539999999999</v>
+        <v>0.520232</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS</t>
+          <t>Model_SOMATOM Definition AS+</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>17.8559</v>
+        <v>10.6053</v>
       </c>
       <c r="C37" t="n">
-        <v>-31.3776</v>
+        <v>-29.2984</v>
       </c>
       <c r="D37" t="n">
-        <v>67.0894</v>
+        <v>50.5091</v>
       </c>
       <c r="E37" t="n">
-        <v>25.0946</v>
+        <v>20.3392</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7115</v>
+        <v>0.5214</v>
       </c>
       <c r="G37" t="n">
-        <v>0.476885</v>
+        <v>0.602166</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition AS+</t>
+          <t>Model_SOMATOM Definition Edge</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>9.8218</v>
+        <v>18.8148</v>
       </c>
       <c r="C38" t="n">
-        <v>-30.3824</v>
+        <v>-24.8242</v>
       </c>
       <c r="D38" t="n">
-        <v>50.0261</v>
+        <v>62.4538</v>
       </c>
       <c r="E38" t="n">
-        <v>20.4923</v>
+        <v>22.2431</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4793</v>
+        <v>0.8459</v>
       </c>
       <c r="G38" t="n">
-        <v>0.631817</v>
+        <v>0.39779</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Edge</t>
+          <t>Model_SOMATOM Definition Flash</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>17.656</v>
+        <v>13.2591</v>
       </c>
       <c r="C39" t="n">
-        <v>-26.316</v>
+        <v>-26.6014</v>
       </c>
       <c r="D39" t="n">
-        <v>61.628</v>
+        <v>53.1196</v>
       </c>
       <c r="E39" t="n">
-        <v>22.4128</v>
+        <v>20.3172</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.6526</v>
       </c>
       <c r="G39" t="n">
-        <v>0.430988</v>
+        <v>0.514133</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Definition Flash</t>
+          <t>Model_SOMATOM Drive</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>13.2764</v>
+        <v>26.1603</v>
       </c>
       <c r="C40" t="n">
-        <v>-26.8789</v>
+        <v>-30.0437</v>
       </c>
       <c r="D40" t="n">
-        <v>53.4317</v>
+        <v>82.3642</v>
       </c>
       <c r="E40" t="n">
-        <v>20.4674</v>
+        <v>28.6475</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.9132</v>
       </c>
       <c r="G40" t="n">
-        <v>0.51668</v>
+        <v>0.36133</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Drive</t>
+          <t>Model_SOMATOM Emotion 16</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.4251</v>
+        <v>34.3709</v>
       </c>
       <c r="C41" t="n">
-        <v>-30.1949</v>
+        <v>-21.9065</v>
       </c>
       <c r="D41" t="n">
-        <v>83.04510000000001</v>
+        <v>90.6484</v>
       </c>
       <c r="E41" t="n">
-        <v>28.8595</v>
+        <v>28.6849</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9156</v>
+        <v>1.1982</v>
       </c>
       <c r="G41" t="n">
-        <v>0.360034</v>
+        <v>0.231064</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Emotion 16</t>
+          <t>Model_SOMATOM Force</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>34.3898</v>
+        <v>18.1481</v>
       </c>
       <c r="C42" t="n">
-        <v>-22.3038</v>
+        <v>-21.7488</v>
       </c>
       <c r="D42" t="n">
-        <v>91.0834</v>
+        <v>58.0451</v>
       </c>
       <c r="E42" t="n">
-        <v>28.897</v>
+        <v>20.3357</v>
       </c>
       <c r="F42" t="n">
-        <v>1.1901</v>
+        <v>0.8924</v>
       </c>
       <c r="G42" t="n">
-        <v>0.234247</v>
+        <v>0.372341</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Force</t>
+          <t>Model_SOMATOM Perspective</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>18.3999</v>
+        <v>9.957800000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>-21.7922</v>
+        <v>-32.5484</v>
       </c>
       <c r="D43" t="n">
-        <v>58.592</v>
+        <v>52.464</v>
       </c>
       <c r="E43" t="n">
-        <v>20.4861</v>
+        <v>21.6657</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8982</v>
+        <v>0.4596</v>
       </c>
       <c r="G43" t="n">
-        <v>0.369277</v>
+        <v>0.645877</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Perspective</t>
+          <t>Model_SOMATOM Scope</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>10.378</v>
+        <v>16.1161</v>
       </c>
       <c r="C44" t="n">
-        <v>-32.4432</v>
+        <v>-29.8073</v>
       </c>
       <c r="D44" t="n">
-        <v>53.1993</v>
+        <v>62.0396</v>
       </c>
       <c r="E44" t="n">
-        <v>21.8262</v>
+        <v>23.4075</v>
       </c>
       <c r="F44" t="n">
-        <v>0.4755</v>
+        <v>0.6885</v>
       </c>
       <c r="G44" t="n">
-        <v>0.634527</v>
+        <v>0.491266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Model_SOMATOM Scope</t>
+          <t>Model_SOMATOM go.Top</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>16.0454</v>
+        <v>-7.9857</v>
       </c>
       <c r="C45" t="n">
-        <v>-30.218</v>
+        <v>-64.49930000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>62.3087</v>
+        <v>48.5279</v>
       </c>
       <c r="E45" t="n">
-        <v>23.5807</v>
+        <v>28.8053</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6804</v>
+        <v>-0.2772</v>
       </c>
       <c r="G45" t="n">
-        <v>0.496352</v>
+        <v>0.781651</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Model_SOMATOM go.Top</t>
+          <t>Model_Scope</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>-4.5583</v>
+        <v>23.5849</v>
       </c>
       <c r="C46" t="n">
-        <v>-61.5422</v>
+        <v>-32.6461</v>
       </c>
       <c r="D46" t="n">
-        <v>52.4256</v>
+        <v>79.8158</v>
       </c>
       <c r="E46" t="n">
-        <v>29.045</v>
+        <v>28.6613</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.1569</v>
+        <v>0.8229</v>
       </c>
       <c r="G46" t="n">
-        <v>0.875318</v>
+        <v>0.410736</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Model_Scope</t>
+          <t>Model_Sensation 16</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24.9213</v>
+        <v>41.363</v>
       </c>
       <c r="C47" t="n">
-        <v>-31.7336</v>
+        <v>-14.8506</v>
       </c>
       <c r="D47" t="n">
-        <v>81.5761</v>
+        <v>97.5766</v>
       </c>
       <c r="E47" t="n">
-        <v>28.8773</v>
+        <v>28.6524</v>
       </c>
       <c r="F47" t="n">
-        <v>0.863</v>
+        <v>1.4436</v>
       </c>
       <c r="G47" t="n">
-        <v>0.388305</v>
+        <v>0.149105</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Model_Sensation 16</t>
+          <t>Model_Sensation 64</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>42.1787</v>
+        <v>4.9283</v>
       </c>
       <c r="C48" t="n">
-        <v>-14.4548</v>
+        <v>-35.1726</v>
       </c>
       <c r="D48" t="n">
-        <v>98.8121</v>
+        <v>45.0291</v>
       </c>
       <c r="E48" t="n">
-        <v>28.8664</v>
+        <v>20.4396</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4612</v>
+        <v>0.2411</v>
       </c>
       <c r="G48" t="n">
-        <v>0.144228</v>
+        <v>0.809508</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Model_Sensation 64</t>
+          <t>Model_Sensation Open</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>5.3685</v>
+        <v>24.7182</v>
       </c>
       <c r="C49" t="n">
-        <v>-35.0302</v>
+        <v>-18.9265</v>
       </c>
       <c r="D49" t="n">
-        <v>45.7673</v>
+        <v>68.363</v>
       </c>
       <c r="E49" t="n">
-        <v>20.5915</v>
+        <v>22.246</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2607</v>
+        <v>1.1111</v>
       </c>
       <c r="G49" t="n">
-        <v>0.794356</v>
+        <v>0.266731</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Model_Sensation Open</t>
+          <t>Model_Spirit</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26.8656</v>
+        <v>-1.5877</v>
       </c>
       <c r="C50" t="n">
-        <v>-17.1282</v>
+        <v>-57.8586</v>
       </c>
       <c r="D50" t="n">
-        <v>70.8593</v>
+        <v>54.6832</v>
       </c>
       <c r="E50" t="n">
-        <v>22.4239</v>
+        <v>28.6816</v>
       </c>
       <c r="F50" t="n">
-        <v>1.1981</v>
+        <v>-0.0554</v>
       </c>
       <c r="G50" t="n">
-        <v>0.23112</v>
+        <v>0.955864</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Model_Spirit</t>
+          <t>Model_Supria</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2108</v>
+        <v>-1.3016</v>
       </c>
       <c r="C51" t="n">
-        <v>-56.907</v>
+        <v>-57.6343</v>
       </c>
       <c r="D51" t="n">
-        <v>56.4853</v>
+        <v>55.0312</v>
       </c>
       <c r="E51" t="n">
-        <v>28.8983</v>
+        <v>28.7132</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.0073</v>
+        <v>-0.0453</v>
       </c>
       <c r="G51" t="n">
-        <v>0.99418</v>
+        <v>0.963851</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Model_Supria</t>
+          <t>Model_iCT 256</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3.5152</v>
+        <v>10.402</v>
       </c>
       <c r="C52" t="n">
-        <v>-53.3487</v>
+        <v>-29.4446</v>
       </c>
       <c r="D52" t="n">
-        <v>60.3792</v>
+        <v>50.2485</v>
       </c>
       <c r="E52" t="n">
-        <v>28.9839</v>
+        <v>20.31</v>
       </c>
       <c r="F52" t="n">
-        <v>0.1213</v>
+        <v>0.5122</v>
       </c>
       <c r="G52" t="n">
-        <v>0.903488</v>
+        <v>0.608632</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Model_iCT 256</t>
+          <t>Model_iCT SP</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>10.1524</v>
+        <v>-28.7501</v>
       </c>
       <c r="C53" t="n">
-        <v>-29.9896</v>
+        <v>-85.0462</v>
       </c>
       <c r="D53" t="n">
-        <v>50.2943</v>
+        <v>27.5459</v>
       </c>
       <c r="E53" t="n">
-        <v>20.4606</v>
+        <v>28.6944</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4962</v>
+        <v>-1.0019</v>
       </c>
       <c r="G53" t="n">
-        <v>0.619849</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Model_iCT SP</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-29.9678</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-86.6871</v>
-      </c>
-      <c r="D54" t="n">
-        <v>26.7515</v>
-      </c>
-      <c r="E54" t="n">
-        <v>28.9102</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-1.0366</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.300135</v>
+        <v>0.316571</v>
       </c>
     </row>
   </sheetData>
@@ -2160,7 +2104,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5833</v>
+        <v>0.5856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -2175,7 +2119,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5654</v>
+        <v>0.5682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2190,7 +2134,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.7277</v>
+        <v>33.7198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -2220,7 +2164,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11306.82</v>
+        <v>11287.17</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -2235,7 +2179,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11579.56</v>
+        <v>11554.76</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -2250,7 +2194,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19.9716</v>
+        <v>19.8331</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -2265,7 +2209,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.676</v>
+        <v>14.6325</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -2280,7 +2224,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5444</v>
+        <v>0.5396</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2295,7 +2239,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0417</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2321,7 +2265,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2336,7 +2280,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9668</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2351,7 +2295,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2379,7 +2323,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>98.8788</v>
+        <v>118.7735</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2394,7 +2338,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>9.6e-05</v>
+        <v>0</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2422,7 +2366,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.96</v>
+        <v>0.9959</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2438,7 +2382,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>정상</t>
+          <t>자기상관 주의</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
@@ -2450,7 +2394,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>367.8</v>
+        <v>305.62</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
